--- a/output/Data and Chart Outputs/denmark_energinet_load_daily.xlsx
+++ b/output/Data and Chart Outputs/denmark_energinet_load_daily.xlsx
@@ -768,7 +768,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 13:16 UTC; 2021-01-01 to 2026-09-07</t>
+          <t>2026-10-04 13:19 UTC; 2021-01-01 to 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/denmark_energinet_load_daily.xlsx
+++ b/output/Data and Chart Outputs/denmark_energinet_load_daily.xlsx
@@ -155,7 +155,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Denmark consumption, production and net imports (Energinet settlement) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Denmark consumption, production and net imports (Energinet settlement) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -191,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -263,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$69</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -299,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$69</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,7 +769,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 13:19 UTC; 2021-01-01 to 2026-09-07</t>
+          <t>2026-10-28 00:56 UTC; 2021-01-01 to 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -783,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -841,10 +842,10 @@
         <v>3244.5223</v>
       </c>
       <c r="C3" t="n">
-        <v>3241.2912</v>
+        <v>3241.291199999999</v>
       </c>
       <c r="D3" t="n">
-        <v>3.230800000000001</v>
+        <v>3.230799999999995</v>
       </c>
       <c r="E3" t="n">
         <v>132.7122</v>
@@ -858,7 +859,7 @@
         <v>3310.9167</v>
       </c>
       <c r="C4" t="n">
-        <v>3103.4426</v>
+        <v>3103.442599999999</v>
       </c>
       <c r="D4" t="n">
         <v>207.4742</v>
@@ -889,7 +890,7 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>2899.2742</v>
+        <v>2899.274200000001</v>
       </c>
       <c r="C6" t="n">
         <v>2167.0042</v>
@@ -912,7 +913,7 @@
         <v>1828.0959</v>
       </c>
       <c r="D7" t="n">
-        <v>886.8883000000001</v>
+        <v>886.8883</v>
       </c>
       <c r="E7" t="n">
         <v>43.2822</v>
@@ -943,13 +944,13 @@
         <v>2787.9406</v>
       </c>
       <c r="C9" t="n">
-        <v>2179.3156</v>
+        <v>2179.315599999999</v>
       </c>
       <c r="D9" t="n">
-        <v>608.6253</v>
+        <v>608.6252999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>58.5106</v>
+        <v>58.51059999999999</v>
       </c>
     </row>
     <row r="10">
@@ -957,16 +958,16 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>2820.9994</v>
+        <v>2820.999399999999</v>
       </c>
       <c r="C10" t="n">
         <v>2183.7406</v>
       </c>
       <c r="D10" t="n">
-        <v>637.2589</v>
+        <v>637.2589000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>62.5912</v>
+        <v>62.59120000000001</v>
       </c>
     </row>
     <row r="11">
@@ -994,7 +995,7 @@
         <v>3244.9202</v>
       </c>
       <c r="C12" t="n">
-        <v>3067.2254</v>
+        <v>3067.225399999999</v>
       </c>
       <c r="D12" t="n">
         <v>177.6945</v>
@@ -1025,13 +1026,13 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>3530.6298</v>
+        <v>3530.629799999999</v>
       </c>
       <c r="C14" t="n">
         <v>3939.9431</v>
       </c>
       <c r="D14" t="n">
-        <v>-409.3132</v>
+        <v>-409.3131999999999</v>
       </c>
       <c r="E14" t="n">
         <v>202.5743</v>
@@ -1059,13 +1060,13 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>3249.831</v>
+        <v>3249.831000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>3181.003</v>
+        <v>3181.003000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>68.8283</v>
+        <v>68.82829999999998</v>
       </c>
       <c r="E16" t="n">
         <v>111.6212</v>
@@ -1079,7 +1080,7 @@
         <v>2938.1329</v>
       </c>
       <c r="C17" t="n">
-        <v>2827.7681</v>
+        <v>2827.768099999999</v>
       </c>
       <c r="D17" t="n">
         <v>110.3647</v>
@@ -1096,13 +1097,13 @@
         <v>2836.7857</v>
       </c>
       <c r="C18" t="n">
-        <v>2586.2847</v>
+        <v>2586.284699999999</v>
       </c>
       <c r="D18" t="n">
         <v>250.5005</v>
       </c>
       <c r="E18" t="n">
-        <v>88.87389999999999</v>
+        <v>88.87390000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1116,7 +1117,7 @@
         <v>1921.5402</v>
       </c>
       <c r="D19" t="n">
-        <v>778.5263</v>
+        <v>778.5262999999999</v>
       </c>
       <c r="E19" t="n">
         <v>61.187</v>
@@ -1127,13 +1128,13 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>2616.6694</v>
+        <v>2616.669399999999</v>
       </c>
       <c r="C20" t="n">
         <v>2580.5891</v>
       </c>
       <c r="D20" t="n">
-        <v>36.07999999999999</v>
+        <v>36.08</v>
       </c>
       <c r="E20" t="n">
         <v>56.2118</v>
@@ -1164,13 +1165,13 @@
         <v>2648.3008</v>
       </c>
       <c r="C22" t="n">
-        <v>2476.336</v>
+        <v>2476.335999999999</v>
       </c>
       <c r="D22" t="n">
         <v>171.9649</v>
       </c>
       <c r="E22" t="n">
-        <v>64.2054</v>
+        <v>64.20540000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1195,13 +1196,13 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>3054.1181</v>
+        <v>3054.118100000001</v>
       </c>
       <c r="C24" t="n">
         <v>3224.29</v>
       </c>
       <c r="D24" t="n">
-        <v>-170.1719</v>
+        <v>-170.1718999999999</v>
       </c>
       <c r="E24" t="n">
         <v>194.761</v>
@@ -1286,7 +1287,7 @@
         <v>2828.8585</v>
       </c>
       <c r="D29" t="n">
-        <v>6.697300000000013</v>
+        <v>6.697300000000003</v>
       </c>
       <c r="E29" t="n">
         <v>178.1333</v>
@@ -1297,7 +1298,7 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>2807.9979</v>
+        <v>2807.997899999999</v>
       </c>
       <c r="C30" t="n">
         <v>2688.0861</v>
@@ -1323,7 +1324,7 @@
         <v>727.8553000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>54.3514</v>
+        <v>54.35140000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1340,7 +1341,7 @@
         <v>6.192</v>
       </c>
       <c r="E32" t="n">
-        <v>74.4021</v>
+        <v>74.40209999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1371,10 +1372,10 @@
         <v>2092.8364</v>
       </c>
       <c r="D34" t="n">
-        <v>643.3359</v>
+        <v>643.3358999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>98.44710000000001</v>
+        <v>98.44709999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1391,7 +1392,7 @@
         <v>428.1353999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>280.5564</v>
+        <v>280.5563999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1399,13 +1400,13 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>3406.4887</v>
+        <v>3406.488700000001</v>
       </c>
       <c r="C36" t="n">
         <v>2798.4033</v>
       </c>
       <c r="D36" t="n">
-        <v>608.0853000000001</v>
+        <v>608.0853</v>
       </c>
       <c r="E36" t="n">
         <v>242.2343</v>
@@ -1416,7 +1417,7 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>3687.2948</v>
+        <v>3687.294799999999</v>
       </c>
       <c r="C37" t="n">
         <v>3584.833</v>
@@ -1425,7 +1426,7 @@
         <v>102.4612</v>
       </c>
       <c r="E37" t="n">
-        <v>357.0012</v>
+        <v>357.0011999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1450,7 +1451,7 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>3361.2543</v>
+        <v>3361.254299999999</v>
       </c>
       <c r="C39" t="n">
         <v>3492.6016</v>
@@ -1470,10 +1471,10 @@
         <v>3344.5526</v>
       </c>
       <c r="C40" t="n">
-        <v>3343.3178</v>
+        <v>3343.317799999999</v>
       </c>
       <c r="D40" t="n">
-        <v>1.234699999999983</v>
+        <v>1.234700000000006</v>
       </c>
       <c r="E40" t="n">
         <v>203.0612</v>
@@ -1507,7 +1508,7 @@
         <v>2532.3153</v>
       </c>
       <c r="D42" t="n">
-        <v>402.2803</v>
+        <v>402.2803000000001</v>
       </c>
       <c r="E42" t="n">
         <v>149.3303</v>
@@ -1524,7 +1525,7 @@
         <v>2355.2585</v>
       </c>
       <c r="D43" t="n">
-        <v>491.99</v>
+        <v>491.9900000000001</v>
       </c>
       <c r="E43" t="n">
         <v>164.0445</v>
@@ -1535,10 +1536,10 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>2735.3306</v>
+        <v>2735.330600000001</v>
       </c>
       <c r="C44" t="n">
-        <v>2319.7335</v>
+        <v>2319.733499999999</v>
       </c>
       <c r="D44" t="n">
         <v>415.5975</v>
@@ -1569,7 +1570,7 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>2905.5595</v>
+        <v>2905.559499999999</v>
       </c>
       <c r="C46" t="n">
         <v>2230.1404</v>
@@ -1586,16 +1587,16 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>3251.597</v>
+        <v>3251.597000000001</v>
       </c>
       <c r="C47" t="n">
         <v>2920.1938</v>
       </c>
       <c r="D47" t="n">
-        <v>331.4028</v>
+        <v>331.4028000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>182.5709</v>
+        <v>182.5708999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1657,7 +1658,7 @@
         <v>3480.4488</v>
       </c>
       <c r="C51" t="n">
-        <v>2874.8012</v>
+        <v>2874.801200000001</v>
       </c>
       <c r="D51" t="n">
         <v>605.6477</v>
@@ -1671,7 +1672,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>3593.8028</v>
+        <v>3593.802799999999</v>
       </c>
       <c r="C52" t="n">
         <v>3190.7929</v>
@@ -1691,7 +1692,7 @@
         <v>3133.9439</v>
       </c>
       <c r="C53" t="n">
-        <v>2197.6642</v>
+        <v>2197.664200000001</v>
       </c>
       <c r="D53" t="n">
         <v>936.2800999999999</v>
@@ -1711,7 +1712,7 @@
         <v>2557.2917</v>
       </c>
       <c r="D54" t="n">
-        <v>703.6269</v>
+        <v>703.6268999999999</v>
       </c>
       <c r="E54" t="n">
         <v>267.0986</v>
@@ -1745,7 +1746,7 @@
         <v>2084.5601</v>
       </c>
       <c r="D56" t="n">
-        <v>811.6565000000001</v>
+        <v>811.6565000000002</v>
       </c>
       <c r="E56" t="n">
         <v>125.0458</v>
@@ -1756,13 +1757,13 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>3110.4624</v>
+        <v>3110.462399999999</v>
       </c>
       <c r="C57" t="n">
         <v>2214.627</v>
       </c>
       <c r="D57" t="n">
-        <v>895.8355</v>
+        <v>895.8354999999999</v>
       </c>
       <c r="E57" t="n">
         <v>152.2822</v>
@@ -1779,10 +1780,10 @@
         <v>2551.0985</v>
       </c>
       <c r="D58" t="n">
-        <v>597.6429000000001</v>
+        <v>597.6429000000002</v>
       </c>
       <c r="E58" t="n">
-        <v>207.7347</v>
+        <v>207.7346999999999</v>
       </c>
     </row>
     <row r="59">
@@ -1810,7 +1811,7 @@
         <v>3667.5996</v>
       </c>
       <c r="C60" t="n">
-        <v>3132.8091</v>
+        <v>3132.809100000001</v>
       </c>
       <c r="D60" t="n">
         <v>534.7910000000001</v>
@@ -1827,10 +1828,10 @@
         <v>3801.6758</v>
       </c>
       <c r="C61" t="n">
-        <v>3298.275</v>
+        <v>3298.275000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>503.4013</v>
+        <v>503.4012999999999</v>
       </c>
       <c r="E61" t="n">
         <v>236.0612</v>
@@ -1847,7 +1848,7 @@
         <v>4043.5973</v>
       </c>
       <c r="D62" t="n">
-        <v>331.8133999999999</v>
+        <v>331.8134</v>
       </c>
       <c r="E62" t="n">
         <v>276.6497</v>
@@ -1875,13 +1876,13 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>3882.4556</v>
+        <v>3882.455600000001</v>
       </c>
       <c r="C64" t="n">
         <v>3205.7538</v>
       </c>
       <c r="D64" t="n">
-        <v>676.7019</v>
+        <v>676.7018999999999</v>
       </c>
       <c r="E64" t="n">
         <v>297.7468</v>
@@ -1901,7 +1902,7 @@
         <v>613.7021999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>283.9946</v>
+        <v>283.9945999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1912,10 +1913,10 @@
         <v>3303.5472</v>
       </c>
       <c r="C66" t="n">
-        <v>2660.3584</v>
+        <v>2660.358400000001</v>
       </c>
       <c r="D66" t="n">
-        <v>643.1888</v>
+        <v>643.1887999999999</v>
       </c>
       <c r="E66" t="n">
         <v>163.7999</v>
@@ -1929,10 +1930,10 @@
         <v>3223.9412</v>
       </c>
       <c r="C67" t="n">
-        <v>2409.9685</v>
+        <v>2409.968499999999</v>
       </c>
       <c r="D67" t="n">
-        <v>813.9723</v>
+        <v>813.9722999999998</v>
       </c>
       <c r="E67" t="n">
         <v>141.5174</v>
@@ -1943,7 +1944,7 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>3187.2347</v>
+        <v>3187.234699999999</v>
       </c>
       <c r="C68" t="n">
         <v>3071.089</v>
@@ -1963,13 +1964,30 @@
         <v>3305.5113</v>
       </c>
       <c r="C69" t="n">
-        <v>3003.3945</v>
+        <v>3003.394499999999</v>
       </c>
       <c r="D69" t="n">
-        <v>302.1168</v>
+        <v>302.1168000000001</v>
       </c>
       <c r="E69" t="n">
         <v>125.8478</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3269.1251</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3223.2354</v>
+      </c>
+      <c r="D70" t="n">
+        <v>45.88939999999999</v>
+      </c>
+      <c r="E70" t="n">
+        <v>143.6737</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2077"/>
+  <dimension ref="A1:F2117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43404,19 +43422,19 @@
         <v>46266</v>
       </c>
       <c r="B2071" t="n">
-        <v>112819.1</v>
+        <v>109680.7</v>
       </c>
       <c r="C2071" t="n">
-        <v>5099.7</v>
+        <v>4594.9</v>
       </c>
       <c r="D2071" t="n">
-        <v>98560.7</v>
+        <v>95422.3</v>
       </c>
       <c r="E2071" t="n">
         <v>14258.4</v>
       </c>
       <c r="F2071" t="n">
-        <v>7091</v>
+        <v>7065.8</v>
       </c>
     </row>
     <row r="2072">
@@ -43424,19 +43442,19 @@
         <v>46267</v>
       </c>
       <c r="B2072" t="n">
-        <v>110957.6</v>
+        <v>107880.1</v>
       </c>
       <c r="C2072" t="n">
-        <v>3262.5</v>
+        <v>2572.5</v>
       </c>
       <c r="D2072" t="n">
-        <v>100461.7</v>
+        <v>97384.10000000001</v>
       </c>
       <c r="E2072" t="n">
         <v>10495.9</v>
       </c>
       <c r="F2072" t="n">
-        <v>7175.3</v>
+        <v>6830.8</v>
       </c>
     </row>
     <row r="2073">
@@ -43444,19 +43462,19 @@
         <v>46268</v>
       </c>
       <c r="B2073" t="n">
-        <v>117908.6</v>
+        <v>115431.7</v>
       </c>
       <c r="C2073" t="n">
-        <v>5635.3</v>
+        <v>4914.6</v>
       </c>
       <c r="D2073" t="n">
-        <v>105435.6</v>
+        <v>102958.8</v>
       </c>
       <c r="E2073" t="n">
         <v>12472.9</v>
       </c>
       <c r="F2073" t="n">
-        <v>8158</v>
+        <v>8136.5</v>
       </c>
     </row>
     <row r="2074">
@@ -43464,19 +43482,19 @@
         <v>46269</v>
       </c>
       <c r="B2074" t="n">
-        <v>112330.2</v>
+        <v>109892</v>
       </c>
       <c r="C2074" t="n">
-        <v>4714.6</v>
+        <v>3983.1</v>
       </c>
       <c r="D2074" t="n">
-        <v>95353.8</v>
+        <v>92915.60000000001</v>
       </c>
       <c r="E2074" t="n">
         <v>16976.3</v>
       </c>
       <c r="F2074" t="n">
-        <v>8397.6</v>
+        <v>8361.9</v>
       </c>
     </row>
     <row r="2075">
@@ -43484,19 +43502,19 @@
         <v>46270</v>
       </c>
       <c r="B2075" t="n">
-        <v>116983</v>
+        <v>113246.8</v>
       </c>
       <c r="C2075" t="n">
-        <v>14922.5</v>
+        <v>14523.3</v>
       </c>
       <c r="D2075" t="n">
-        <v>143722.3</v>
+        <v>139986.1</v>
       </c>
       <c r="E2075" t="n">
         <v>-26739.3</v>
       </c>
       <c r="F2075" t="n">
-        <v>9087.6</v>
+        <v>9153.200000000001</v>
       </c>
     </row>
     <row r="2076">
@@ -43504,19 +43522,19 @@
         <v>46271</v>
       </c>
       <c r="B2076" t="n">
-        <v>105794.2</v>
+        <v>102138.9</v>
       </c>
       <c r="C2076" t="n">
-        <v>9694.9</v>
+        <v>9266.200000000001</v>
       </c>
       <c r="D2076" t="n">
-        <v>107680.7</v>
+        <v>104025.4</v>
       </c>
       <c r="E2076" t="n">
         <v>-1886.5</v>
       </c>
       <c r="F2076" t="n">
-        <v>7308.2</v>
+        <v>7373.7</v>
       </c>
     </row>
     <row r="2077">
@@ -43524,19 +43542,819 @@
         <v>46272</v>
       </c>
       <c r="B2077" t="n">
-        <v>111847.8</v>
+        <v>108330.7</v>
       </c>
       <c r="C2077" t="n">
-        <v>5570.4</v>
+        <v>4628.2</v>
       </c>
       <c r="D2077" t="n">
-        <v>122361.3</v>
+        <v>118844.2</v>
       </c>
       <c r="E2077" t="n">
         <v>-10513.5</v>
       </c>
       <c r="F2077" t="n">
-        <v>6333.3</v>
+        <v>6508.9</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="4" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>110307.7</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>4809.8</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>79552</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>30755.6</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>6684.8</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="4" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>109484.1</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>2382.6</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>117351</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>-7867</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>7220.7</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>106459.4</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>2417.3</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>103598.4</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>2861</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>6665.8</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>104093.6</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>1940.1</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>93758.10000000001</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>10335.5</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>6456.6</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>102924.3</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>6473.6</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>86158.10000000001</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>16766.1</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>6697</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="4" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>94068.3</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>1286.2</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>98562.7</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>-4494.4</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>6538.2</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="4" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>103647.3</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>1135.7</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>83408.8</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>20238.5</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>6100.1</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="4" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>111487.1</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>3707</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>124188.4</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>-12701.4</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>7537.9</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="4" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>108879.5</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>1550</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>146954.3</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>-38074.8</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>7618.7</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2087" t="n">
+        <v>117609.6</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>6770.3</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>120754.6</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>-3145</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>8096.4</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>114321.3</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>6334.2</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>138658.2</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>-24336.9</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>8412.6</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="4" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>116599.1</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>13840.1</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>120411.5</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>-3812.4</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>8968.5</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="4" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>113885.4</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>14213</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>135370.8</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>-21485.3</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>9475.4</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>117849.8</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>8493.200000000001</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>152206.7</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>-34356.8</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>9116.1</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B2092" t="n">
+        <v>106477.3</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>62515.1</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>43962.3</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>6307.6</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2093" t="n">
+        <v>108577.9</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>1325.5</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>72811.10000000001</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>35766.7</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>7314.7</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>110893.7</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>1557.5</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>102360.8</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>8532.9</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>7676.4</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>107753.5</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>2796.2</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>92464.8</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>15288.7</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>6831.6</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="4" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>99221.60000000001</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>3241.4</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>89442.39999999999</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>9779.299999999999</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>6443.2</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>108764.6</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>7807.4</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>112652.2</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>-3887.7</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>8222.5</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="4" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>104072.6</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>667.4</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>76457.60000000001</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>27615</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>6378</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>109478.6</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>2111.7</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>95767</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>13711.7</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>6954.1</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>115667.9</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>3217.8</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>166294.3</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>-50626.4</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>8476.6</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>107316.5</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>613.1</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>125079.6</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>-17763.1</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>7052.4</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>105129.4</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>447.9</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>81420.5</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>23708.9</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>6243.6</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>97911</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>1724.9</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>111894.9</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>-13983.9</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>6640.2</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>100777.2</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>3505.6</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>102069</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>-1291.8</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>6921</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>116001.4</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>3833.9</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>152666.4</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>-36665</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>8899.299999999999</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>107203.3</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>759.3</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>80591.3</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>26612</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>6452.1</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>109669.8</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>780.5</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>76257</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>33412.8</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>6607.1</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>119294.1</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>3327.8</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>136670.7</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>-17376.6</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>9174.9</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>122930.1</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>7748.5</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>102092.2</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>20837.9</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>9273.4</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>117102.3</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>12491.7</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>94884.8</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>22217.6</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>8343.4</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>103870.3</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>4137.9</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>78910.10000000001</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>24960.2</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>7172.8</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>112218.8</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>1656.5</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>88570.7</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>23648</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>6591.8</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>120767.7</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>4290.4</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>150960</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>-30192.3</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>9204.799999999999</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>117281.2</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>3619.5</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>150884.7</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>-33603.5</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>8288.4</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>115849.4</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>1757.5</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>145868.8</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>-30019.4</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>8184.7</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>109082.1</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>1254.9</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>100226.2</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>8855.9</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>6864.5</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>106519.2</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>2871.7</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>148016.3</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>-41497.2</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>8099.7</v>
       </c>
     </row>
   </sheetData>
